--- a/testFile/case/LoginExcel.xlsx
+++ b/testFile/case/LoginExcel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16725" windowHeight="7215" activeTab="4"/>
+    <workbookView windowWidth="20317" windowHeight="9727" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
@@ -13,12 +13,25 @@
     <sheet name="position" sheetId="4" r:id="rId4"/>
     <sheet name="emp" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="187">
   <si>
     <t>测试用例编号</t>
   </si>
@@ -78,6 +91,26 @@
   </si>
   <si>
     <t>"retmsg":"操作成功"</t>
+  </si>
+  <si>
+    <t>调度登录验证码获取</t>
+  </si>
+  <si>
+    <t>/buswash/login/admin/code</t>
+  </si>
+  <si>
+    <t>{
+  "account": "liukeke"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": [],
+  "total": null,
+  "success": true
+}</t>
   </si>
   <si>
     <t>登录模块/移动端登录</t>
@@ -216,15 +249,6 @@
   <si>
     <t>{
   "account": "liukeke001"
-}</t>
-  </si>
-  <si>
-    <t>{
-  "retcode": "0",
-  "retmsg": "操作成功",
-  "data": [],
-  "total": null,
-  "success": true
 }</t>
   </si>
   <si>
@@ -1079,7 +1103,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1689,7 +1713,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1698,9 +1722,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2016,7 +2037,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.6814159292035" customWidth="1"/>
@@ -2100,135 +2121,135 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="H3">
-        <v>200</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="139" customHeight="1" spans="1:10">
+    <row r="4" ht="135" customHeight="1" spans="1:10">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4">
+        <v>200</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="H4">
-        <v>200</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="132" customHeight="1" spans="1:10">
+    <row r="5" ht="139" customHeight="1" spans="1:10">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5">
+        <v>200</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="H5">
-        <v>200</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="116" customHeight="1" spans="1:10">
+    <row r="6" ht="132" customHeight="1" spans="1:10">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="H6">
-        <v>200</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="109" customHeight="1" spans="1:10">
+    <row r="7" ht="116" customHeight="1" spans="1:10">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
         <v>38</v>
@@ -2255,59 +2276,59 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" ht="136" customHeight="1" spans="1:10">
+    <row r="8" ht="109" customHeight="1" spans="1:10">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
         <v>43</v>
       </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="H8">
         <v>200</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="129" customHeight="1" spans="1:10">
+    <row r="9" ht="136" customHeight="1" spans="1:10">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="H9">
         <v>200</v>
@@ -2319,35 +2340,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="126" customHeight="1" spans="1:10">
+    <row r="10" ht="129" customHeight="1" spans="1:10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
         <v>50</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
         <v>51</v>
       </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10">
+        <v>200</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="126" customHeight="1" spans="1:10">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H10">
-        <v>200</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="C11" t="s">
         <v>54</v>
       </c>
-      <c r="J10" t="s">
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11">
+        <v>200</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2413,28 +2466,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H2">
         <v>200</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -2445,31 +2498,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H3">
         <v>200</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="161" customHeight="1" spans="1:10">
@@ -2477,28 +2530,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H4">
         <v>200</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -2509,28 +2562,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H5">
         <v>200</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -2597,28 +2650,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H2">
         <v>200</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -2629,28 +2682,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3">
-        <v>200</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -2661,22 +2714,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H4">
         <v>200</v>
@@ -2687,28 +2740,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H5">
         <v>200</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -2719,22 +2772,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H6">
         <v>200</v>
@@ -2745,28 +2798,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H7">
         <v>200</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -2777,22 +2830,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H8">
         <v>200</v>
@@ -2803,28 +2856,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H9">
         <v>200</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -2835,22 +2888,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H10">
         <v>200</v>
@@ -2861,28 +2914,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H11">
         <v>200</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -2893,28 +2946,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H12">
         <v>200</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -2925,28 +2978,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H13">
         <v>200</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -2957,28 +3010,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H14">
         <v>200</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -2989,31 +3042,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H15">
         <v>200</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3077,28 +3130,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H2">
         <v>200</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -3109,22 +3162,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H3">
         <v>200</v>
@@ -3141,22 +3194,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H4">
         <v>200</v>
@@ -3173,28 +3226,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H5">
         <v>200</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -3205,28 +3258,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H6">
         <v>200</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -3237,22 +3290,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H7">
         <v>200</v>
@@ -3269,28 +3322,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H8">
         <v>200</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -3301,19 +3354,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H9">
         <v>200</v>
@@ -3330,28 +3383,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H10">
         <v>200</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -3418,26 +3471,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2">
         <v>200</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -3448,22 +3501,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H3">
         <v>200</v>
@@ -3474,28 +3527,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="H4">
         <v>200</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -3506,28 +3559,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H5">
         <v>200</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -3538,31 +3591,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>181</v>
+      <c r="G6" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="H6">
         <v>200</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>182</v>
+      <c r="I6" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="J6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
